--- a/pipeline_output/HR_2W_H&M.xlsx
+++ b/pipeline_output/HR_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -10750,12 +10750,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12488,12 +12488,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12742,12 +12742,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12859,12 +12859,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13210,12 +13210,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13327,12 +13327,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13952,12 +13952,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14206,12 +14206,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14323,12 +14323,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14577,12 +14577,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14694,12 +14694,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14821,12 +14821,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14948,12 +14948,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15065,12 +15065,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15192,12 +15192,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15573,12 +15573,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15807,12 +15807,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15924,12 +15924,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16041,12 +16041,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16158,12 +16158,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16285,12 +16285,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16666,12 +16666,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16783,12 +16783,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16910,12 +16910,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17037,12 +17037,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17154,12 +17154,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17281,12 +17281,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17408,12 +17408,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17525,12 +17525,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17652,12 +17652,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17779,12 +17779,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17841,7 +17841,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -17896,12 +17896,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -18023,12 +18023,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -18150,12 +18150,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -18277,12 +18277,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -18404,12 +18404,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18466,7 +18466,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -18521,12 +18521,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -18638,12 +18638,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -18755,12 +18755,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -18989,12 +18989,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -19116,12 +19116,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19178,7 +19178,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -19243,12 +19243,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -19370,12 +19370,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -19497,12 +19497,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -19741,12 +19741,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -19868,12 +19868,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -19985,12 +19985,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -20112,12 +20112,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -20239,12 +20239,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -20356,12 +20356,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -20483,12 +20483,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>HARYANA</t>
+          <t>HARYANA, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -20610,12 +20610,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20737,12 +20737,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20864,12 +20864,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20991,12 +20991,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21118,12 +21118,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21245,12 +21245,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21499,12 +21499,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21626,12 +21626,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21743,12 +21743,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21860,12 +21860,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21977,12 +21977,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22094,12 +22094,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22211,12 +22211,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22328,12 +22328,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22562,12 +22562,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22679,12 +22679,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22796,12 +22796,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22913,12 +22913,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -23030,12 +23030,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23147,12 +23147,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23264,12 +23264,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23381,12 +23381,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23498,12 +23498,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
